--- a/data/student.xlsx
+++ b/data/student.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\IdeaProjects\java.b\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61DE8EE9-1A37-4352-9200-C8AEBD173E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0CC64A-426C-4DA3-BC21-4B99478DBD29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53C596C6-DF10-4760-8D8D-6BDFE4E072C8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="16">
   <si>
     <t>학번</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,6 +78,30 @@
   </si>
   <si>
     <t>여</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김박사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>항천문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김일성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김도문</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앙기모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와일드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -585,7 +609,7 @@
         <v>1234571</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
@@ -608,7 +632,7 @@
         <v>1234572</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -631,7 +655,7 @@
         <v>1234573</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -654,7 +678,7 @@
         <v>1234574</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -723,7 +747,7 @@
         <v>1234577</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -769,7 +793,7 @@
         <v>1234579</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
